--- a/posiciones_buscador.xlsx
+++ b/posiciones_buscador.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -102,6 +102,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1040"/>
+  <dimension ref="A1:H1042"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="13.81640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -44042,6 +44043,78 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1041">
+      <c r="A1041" s="6" t="n">
+        <v>7506022304100</v>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>No tiene códigos alternos</t>
+        </is>
+      </c>
+      <c r="C1041" t="n">
+        <v>421</v>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>AGUJA HIPRODERMICA  20 X 38</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H1041" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="6" t="n">
+        <v>7506022304742</v>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>No tiene códigos alternos</t>
+        </is>
+      </c>
+      <c r="C1042" t="n">
+        <v>423</v>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>AGUJAS HIPRODERMICAS 23 X 25</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H1042" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
